--- a/data/crypto.xlsx
+++ b/data/crypto.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:L4"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -405,19 +405,12 @@
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
     <col min="5" max="5" width="12.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="8" width="50.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="50.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
     <col min="11" max="11" width="12.83203125" customWidth="1"/>
     <col min="12" max="12" width="12.83203125" customWidth="1"/>
-    <col min="13" max="13" width="10.83203125" customWidth="1"/>
-    <col min="14" max="14" width="10.83203125" customWidth="1"/>
-    <col min="15" max="15" width="10.83203125" customWidth="1"/>
-    <col min="16" max="16" width="10.83203125" customWidth="1"/>
-    <col min="17" max="17" width="10.83203125" customWidth="1"/>
-    <col min="18" max="18" width="10.83203125" customWidth="1"/>
-    <col min="19" max="19" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -440,43 +433,22 @@
         <v>currentPrice</v>
       </c>
       <c r="G1" t="str">
-        <v>change24h</v>
+        <v>notes</v>
       </c>
       <c r="H1" t="str">
-        <v>notes</v>
+        <v>accountType</v>
       </c>
       <c r="I1" t="str">
-        <v>accountType</v>
+        <v>accountName</v>
       </c>
       <c r="J1" t="str">
-        <v>accountName</v>
+        <v>costBasis</v>
       </c>
       <c r="K1" t="str">
-        <v>costBasis</v>
+        <v>purchaseDate</v>
       </c>
       <c r="L1" t="str">
-        <v>purchaseDate</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Day 1</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Day 2</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Day 3</v>
-      </c>
-      <c r="P1" t="str">
-        <v>Day 4</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>Day 5</v>
-      </c>
-      <c r="R1" t="str">
-        <v>Day 6</v>
-      </c>
-      <c r="S1" t="str">
-        <v>Day 7</v>
+        <v>lastUpdated</v>
       </c>
     </row>
     <row r="2">
@@ -498,44 +470,23 @@
       <c r="F2">
         <v>97500</v>
       </c>
-      <c r="G2">
-        <v>-3.2</v>
+      <c r="G2" t="str">
+        <v>Core crypto position. DCA strategy. Halving cycle thesis.</v>
       </c>
       <c r="H2" t="str">
-        <v>Core crypto position. DCA strategy. Halving cycle thesis.</v>
+        <v>taxable</v>
       </c>
       <c r="I2" t="str">
-        <v>taxable</v>
-      </c>
-      <c r="J2" t="str">
         <v>Coinbase</v>
       </c>
-      <c r="K2">
+      <c r="J2">
         <v>105000</v>
       </c>
+      <c r="K2" t="str">
+        <v>2022-11-15</v>
+      </c>
       <c r="L2" t="str">
-        <v>2022-11-15</v>
-      </c>
-      <c r="M2">
-        <v>101000</v>
-      </c>
-      <c r="N2">
-        <v>99800</v>
-      </c>
-      <c r="O2">
-        <v>98200</v>
-      </c>
-      <c r="P2">
-        <v>99500</v>
-      </c>
-      <c r="Q2">
-        <v>98000</v>
-      </c>
-      <c r="R2">
-        <v>97800</v>
-      </c>
-      <c r="S2">
-        <v>97500</v>
+        <v>2026-02-11</v>
       </c>
     </row>
     <row r="3">
@@ -557,44 +508,23 @@
       <c r="F3">
         <v>3180</v>
       </c>
-      <c r="G3">
-        <v>-1.8</v>
+      <c r="G3" t="str">
+        <v>Layer 1 ecosystem. Staking yield ~4%. Long-term hold.</v>
       </c>
       <c r="H3" t="str">
-        <v>Layer 1 ecosystem. Staking yield ~4%. Long-term hold.</v>
+        <v>taxable</v>
       </c>
       <c r="I3" t="str">
-        <v>taxable</v>
-      </c>
-      <c r="J3" t="str">
         <v>Coinbase</v>
       </c>
-      <c r="K3">
+      <c r="J3">
         <v>55000</v>
       </c>
+      <c r="K3" t="str">
+        <v>2023-01-10</v>
+      </c>
       <c r="L3" t="str">
-        <v>2023-01-10</v>
-      </c>
-      <c r="M3">
-        <v>3280</v>
-      </c>
-      <c r="N3">
-        <v>3250</v>
-      </c>
-      <c r="O3">
-        <v>3220</v>
-      </c>
-      <c r="P3">
-        <v>3200</v>
-      </c>
-      <c r="Q3">
-        <v>3190</v>
-      </c>
-      <c r="R3">
-        <v>3185</v>
-      </c>
-      <c r="S3">
-        <v>3180</v>
+        <v>2026-02-11</v>
       </c>
     </row>
     <row r="4">
@@ -616,49 +546,28 @@
       <c r="F4">
         <v>185</v>
       </c>
-      <c r="G4">
-        <v>2.5</v>
+      <c r="G4" t="str">
+        <v>High-performance L1. DeFi/NFT ecosystem growth.</v>
       </c>
       <c r="H4" t="str">
-        <v>High-performance L1. DeFi/NFT ecosystem growth.</v>
+        <v>taxable</v>
       </c>
       <c r="I4" t="str">
-        <v>taxable</v>
-      </c>
-      <c r="J4" t="str">
         <v>Coinbase</v>
       </c>
-      <c r="K4">
+      <c r="J4">
         <v>9000</v>
       </c>
+      <c r="K4" t="str">
+        <v>2023-08-22</v>
+      </c>
       <c r="L4" t="str">
-        <v>2023-08-22</v>
-      </c>
-      <c r="M4">
-        <v>175</v>
-      </c>
-      <c r="N4">
-        <v>178</v>
-      </c>
-      <c r="O4">
-        <v>180</v>
-      </c>
-      <c r="P4">
-        <v>182</v>
-      </c>
-      <c r="Q4">
-        <v>183</v>
-      </c>
-      <c r="R4">
-        <v>184</v>
-      </c>
-      <c r="S4">
-        <v>185</v>
+        <v>2026-02-11</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/crypto.xlsx
+++ b/data/crypto.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L3"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -462,7 +462,7 @@
         <v>BTC</v>
       </c>
       <c r="D2">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="E2">
         <v>42000</v>
@@ -471,7 +471,7 @@
         <v>97500</v>
       </c>
       <c r="G2" t="str">
-        <v>Core crypto position. DCA strategy. Halving cycle thesis.</v>
+        <v>Small BTC position. Bought during 2022 bear market. Digital gold thesis.</v>
       </c>
       <c r="H2" t="str">
         <v>taxable</v>
@@ -480,13 +480,13 @@
         <v>Coinbase</v>
       </c>
       <c r="J2">
-        <v>105000</v>
+        <v>21000</v>
       </c>
       <c r="K2" t="str">
-        <v>2022-11-15</v>
+        <v>2022-12-01</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-02-11</v>
+        <v>2026-02-12</v>
       </c>
     </row>
     <row r="3">
@@ -500,7 +500,7 @@
         <v>ETH</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>2200</v>
@@ -509,7 +509,7 @@
         <v>3180</v>
       </c>
       <c r="G3" t="str">
-        <v>Layer 1 ecosystem. Staking yield ~4%. Long-term hold.</v>
+        <v>Layer 1 ecosystem. Intellectual interest. Not a "crypto person."</v>
       </c>
       <c r="H3" t="str">
         <v>taxable</v>
@@ -518,56 +518,18 @@
         <v>Coinbase</v>
       </c>
       <c r="J3">
-        <v>55000</v>
+        <v>17600</v>
       </c>
       <c r="K3" t="str">
-        <v>2023-01-10</v>
+        <v>2023-02-10</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-02-11</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>sol</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Solana</v>
-      </c>
-      <c r="C4" t="str">
-        <v>SOL</v>
-      </c>
-      <c r="D4">
-        <v>200</v>
-      </c>
-      <c r="E4">
-        <v>45</v>
-      </c>
-      <c r="F4">
-        <v>185</v>
-      </c>
-      <c r="G4" t="str">
-        <v>High-performance L1. DeFi/NFT ecosystem growth.</v>
-      </c>
-      <c r="H4" t="str">
-        <v>taxable</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Coinbase</v>
-      </c>
-      <c r="J4">
-        <v>9000</v>
-      </c>
-      <c r="K4" t="str">
-        <v>2023-08-22</v>
-      </c>
-      <c r="L4" t="str">
-        <v>2026-02-11</v>
+        <v>2026-02-12</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/crypto.xlsx
+++ b/data/crypto.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -462,7 +462,7 @@
         <v>BTC</v>
       </c>
       <c r="D2">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="E2">
         <v>42000</v>
@@ -471,7 +471,7 @@
         <v>97500</v>
       </c>
       <c r="G2" t="str">
-        <v>Small BTC position. Bought during 2022 bear market. Digital gold thesis.</v>
+        <v>Core crypto position. DCA strategy. Halving cycle thesis.</v>
       </c>
       <c r="H2" t="str">
         <v>taxable</v>
@@ -480,10 +480,10 @@
         <v>Coinbase</v>
       </c>
       <c r="J2">
-        <v>21000</v>
+        <v>50400</v>
       </c>
       <c r="K2" t="str">
-        <v>2022-12-01</v>
+        <v>2022-11-15</v>
       </c>
       <c r="L2" t="str">
         <v>2026-02-12</v>
@@ -500,7 +500,7 @@
         <v>ETH</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E3">
         <v>2200</v>
@@ -509,7 +509,7 @@
         <v>3180</v>
       </c>
       <c r="G3" t="str">
-        <v>Layer 1 ecosystem. Intellectual interest. Not a "crypto person."</v>
+        <v>Layer 1 ecosystem. Staking yield ~4%. Long-term hold.</v>
       </c>
       <c r="H3" t="str">
         <v>taxable</v>
@@ -518,18 +518,56 @@
         <v>Coinbase</v>
       </c>
       <c r="J3">
-        <v>17600</v>
+        <v>33000</v>
       </c>
       <c r="K3" t="str">
-        <v>2023-02-10</v>
+        <v>2023-01-10</v>
       </c>
       <c r="L3" t="str">
+        <v>2026-02-12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>sol</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Solana</v>
+      </c>
+      <c r="C4" t="str">
+        <v>SOL</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4">
+        <v>45</v>
+      </c>
+      <c r="F4">
+        <v>185</v>
+      </c>
+      <c r="G4" t="str">
+        <v>High-performance L1. DeFi/NFT ecosystem growth.</v>
+      </c>
+      <c r="H4" t="str">
+        <v>taxable</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Coinbase</v>
+      </c>
+      <c r="J4">
+        <v>4500</v>
+      </c>
+      <c r="K4" t="str">
+        <v>2023-08-22</v>
+      </c>
+      <c r="L4" t="str">
         <v>2026-02-12</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/crypto.xlsx
+++ b/data/crypto.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L3"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -462,7 +462,7 @@
         <v>BTC</v>
       </c>
       <c r="D2">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="E2">
         <v>42000</v>
@@ -471,7 +471,7 @@
         <v>97500</v>
       </c>
       <c r="G2" t="str">
-        <v>Core crypto position. DCA strategy. Halving cycle thesis.</v>
+        <v>Small BTC position. Bought during 2022 bear market. Digital gold thesis.</v>
       </c>
       <c r="H2" t="str">
         <v>taxable</v>
@@ -480,10 +480,10 @@
         <v>Coinbase</v>
       </c>
       <c r="J2">
-        <v>50400</v>
+        <v>21000</v>
       </c>
       <c r="K2" t="str">
-        <v>2022-11-15</v>
+        <v>2022-12-01</v>
       </c>
       <c r="L2" t="str">
         <v>2026-02-12</v>
@@ -500,7 +500,7 @@
         <v>ETH</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>2200</v>
@@ -509,7 +509,7 @@
         <v>3180</v>
       </c>
       <c r="G3" t="str">
-        <v>Layer 1 ecosystem. Staking yield ~4%. Long-term hold.</v>
+        <v>Layer 1 ecosystem. Intellectual interest. Not a "crypto person."</v>
       </c>
       <c r="H3" t="str">
         <v>taxable</v>
@@ -518,56 +518,18 @@
         <v>Coinbase</v>
       </c>
       <c r="J3">
-        <v>33000</v>
+        <v>17600</v>
       </c>
       <c r="K3" t="str">
-        <v>2023-01-10</v>
+        <v>2023-02-10</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-02-12</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>sol</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Solana</v>
-      </c>
-      <c r="C4" t="str">
-        <v>SOL</v>
-      </c>
-      <c r="D4">
-        <v>100</v>
-      </c>
-      <c r="E4">
-        <v>45</v>
-      </c>
-      <c r="F4">
-        <v>185</v>
-      </c>
-      <c r="G4" t="str">
-        <v>High-performance L1. DeFi/NFT ecosystem growth.</v>
-      </c>
-      <c r="H4" t="str">
-        <v>taxable</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Coinbase</v>
-      </c>
-      <c r="J4">
-        <v>4500</v>
-      </c>
-      <c r="K4" t="str">
-        <v>2023-08-22</v>
-      </c>
-      <c r="L4" t="str">
         <v>2026-02-12</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/crypto.xlsx
+++ b/data/crypto.xlsx
@@ -398,20 +398,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L3"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="50.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -468,7 +454,7 @@
         <v>42000</v>
       </c>
       <c r="F2">
-        <v>97500</v>
+        <v>66927.65</v>
       </c>
       <c r="G2" t="str">
         <v>Small BTC position. Bought during 2022 bear market. Digital gold thesis.</v>
@@ -486,7 +472,7 @@
         <v>2022-12-01</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-13</v>
       </c>
     </row>
     <row r="3">
@@ -506,7 +492,7 @@
         <v>2200</v>
       </c>
       <c r="F3">
-        <v>3180</v>
+        <v>1957.72</v>
       </c>
       <c r="G3" t="str">
         <v>Layer 1 ecosystem. Intellectual interest. Not a "crypto person."</v>
@@ -524,7 +510,7 @@
         <v>2023-02-10</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-02-12</v>
+        <v>2026-02-13</v>
       </c>
     </row>
   </sheetData>

--- a/data/crypto.xlsx
+++ b/data/crypto.xlsx
@@ -397,7 +397,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="50.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -448,16 +462,16 @@
         <v>BTC</v>
       </c>
       <c r="D2">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="E2">
         <v>42000</v>
       </c>
       <c r="F2">
-        <v>66927.65</v>
+        <v>97500</v>
       </c>
       <c r="G2" t="str">
-        <v>Small BTC position. Bought during 2022 bear market. Digital gold thesis.</v>
+        <v>Core crypto position. DCA strategy. Halving cycle thesis.</v>
       </c>
       <c r="H2" t="str">
         <v>taxable</v>
@@ -466,13 +480,13 @@
         <v>Coinbase</v>
       </c>
       <c r="J2">
-        <v>21000</v>
+        <v>50400</v>
       </c>
       <c r="K2" t="str">
-        <v>2022-12-01</v>
+        <v>2022-11-15</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-02-13</v>
+        <v>2026-02-12</v>
       </c>
     </row>
     <row r="3">
@@ -486,16 +500,16 @@
         <v>ETH</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E3">
         <v>2200</v>
       </c>
       <c r="F3">
-        <v>1957.72</v>
+        <v>3180</v>
       </c>
       <c r="G3" t="str">
-        <v>Layer 1 ecosystem. Intellectual interest. Not a "crypto person."</v>
+        <v>Layer 1 ecosystem. Staking yield ~4%. Long-term hold.</v>
       </c>
       <c r="H3" t="str">
         <v>taxable</v>
@@ -504,18 +518,56 @@
         <v>Coinbase</v>
       </c>
       <c r="J3">
-        <v>17600</v>
+        <v>33000</v>
       </c>
       <c r="K3" t="str">
-        <v>2023-02-10</v>
+        <v>2023-01-10</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-02-13</v>
+        <v>2026-02-12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>sol</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Solana</v>
+      </c>
+      <c r="C4" t="str">
+        <v>SOL</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4">
+        <v>45</v>
+      </c>
+      <c r="F4">
+        <v>185</v>
+      </c>
+      <c r="G4" t="str">
+        <v>High-performance L1. DeFi/NFT ecosystem growth.</v>
+      </c>
+      <c r="H4" t="str">
+        <v>taxable</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Coinbase</v>
+      </c>
+      <c r="J4">
+        <v>4500</v>
+      </c>
+      <c r="K4" t="str">
+        <v>2023-08-22</v>
+      </c>
+      <c r="L4" t="str">
+        <v>2026-02-12</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>